--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>134080557</v>
       </c>
       <c r="B8" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>134081400</v>
       </c>
       <c r="B9" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134083560</v>
       </c>
       <c r="B10" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>134083716</v>
       </c>
       <c r="B11" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>134080557</v>
       </c>
       <c r="B8" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>134081400</v>
       </c>
       <c r="B9" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134083560</v>
       </c>
       <c r="B10" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>134083716</v>
       </c>
       <c r="B11" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
